--- a/accountant-skill/Exisitng Accounting Workflow _ reference files/Financial Reports/Financial_Statements.xlsx
+++ b/accountant-skill/Exisitng Accounting Workflow _ reference files/Financial Reports/Financial_Statements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\workspace_accountant\accountant-skill\Exisitng Accounting Workflow _ reference files\Financial Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaung\workspace_accountant\accountant-skill\Exisitng Accounting Workflow _ reference files\Financial Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA113D36-0E91-4BE1-95B2-60CDCB8252D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D532246-AA65-42B8-B360-36223D53E908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement_of_Profit&amp;Loss" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,7 @@
     <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
     <sheet name="Copy of Monthly P&amp;L" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1141,40 +1140,40 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5382,8 +5381,8 @@
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10074,39 +10073,39 @@
     <row r="6" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="28"/>
       <c r="D6" s="29">
-        <f>SUM(D5:D5)</f>
+        <f t="shared" ref="D6:L6" si="0">SUM(D5:D5)</f>
         <v>12876000</v>
       </c>
       <c r="E6" s="29">
-        <f>SUM(E5:E5)</f>
+        <f t="shared" si="0"/>
         <v>38186000</v>
       </c>
       <c r="F6" s="29">
-        <f>SUM(F5:F5)</f>
+        <f t="shared" si="0"/>
         <v>52160000</v>
       </c>
       <c r="G6" s="29">
-        <f>SUM(G5:G5)</f>
+        <f t="shared" si="0"/>
         <v>57481000</v>
       </c>
       <c r="H6" s="29">
-        <f>SUM(H5:H5)</f>
+        <f t="shared" si="0"/>
         <v>33478500</v>
       </c>
       <c r="I6" s="29">
-        <f>SUM(I5:I5)</f>
+        <f t="shared" si="0"/>
         <v>19774500</v>
       </c>
       <c r="J6" s="29">
-        <f>SUM(J5:J5)</f>
+        <f t="shared" si="0"/>
         <v>19759500</v>
       </c>
       <c r="K6" s="29">
-        <f>SUM(K5:K5)</f>
+        <f t="shared" si="0"/>
         <v>25669100</v>
       </c>
       <c r="L6" s="29">
-        <f>SUM(L5:L5)</f>
+        <f t="shared" si="0"/>
         <v>21894000</v>
       </c>
     </row>
@@ -10576,39 +10575,39 @@
     <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="30"/>
       <c r="D25" s="31">
-        <f>SUM(D11:D24)</f>
+        <f t="shared" ref="D25:L25" si="1">SUM(D11:D24)</f>
         <v>11630835.219999993</v>
       </c>
       <c r="E25" s="31">
-        <f>SUM(E11:E24)</f>
+        <f t="shared" si="1"/>
         <v>35800728.840000011</v>
       </c>
       <c r="F25" s="31">
-        <f>SUM(F11:F24)</f>
+        <f t="shared" si="1"/>
         <v>45238168.109999999</v>
       </c>
       <c r="G25" s="31">
-        <f>SUM(G11:G24)</f>
+        <f t="shared" si="1"/>
         <v>48869665.760000013</v>
       </c>
       <c r="H25" s="31">
-        <f>SUM(H11:H24)</f>
+        <f t="shared" si="1"/>
         <v>29203604.869999997</v>
       </c>
       <c r="I25" s="31">
-        <f>SUM(I11:I24)</f>
+        <f t="shared" si="1"/>
         <v>17914424.629999995</v>
       </c>
       <c r="J25" s="31">
-        <f>SUM(J11:J24)</f>
+        <f t="shared" si="1"/>
         <v>20165754.34</v>
       </c>
       <c r="K25" s="31">
-        <f>SUM(K11:K24)</f>
+        <f t="shared" si="1"/>
         <v>26546845.050000004</v>
       </c>
       <c r="L25" s="31">
-        <f>SUM(L11:L24)</f>
+        <f t="shared" si="1"/>
         <v>21981284.84</v>
       </c>
     </row>
@@ -10983,39 +10982,39 @@
     <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="28"/>
       <c r="D40" s="29">
-        <f t="shared" ref="D40:L40" si="0">SUM(D30:D39)</f>
+        <f t="shared" ref="D40:L40" si="2">SUM(D30:D39)</f>
         <v>685666.67</v>
       </c>
       <c r="E40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>766027.03</v>
       </c>
       <c r="F40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2306778.67</v>
       </c>
       <c r="G40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1530079.67</v>
       </c>
       <c r="H40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>933983</v>
       </c>
       <c r="I40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>931323</v>
       </c>
       <c r="J40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2638822.5</v>
       </c>
       <c r="K40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2512630</v>
       </c>
       <c r="L40" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1280715</v>
       </c>
     </row>
@@ -11127,39 +11126,39 @@
     <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="28"/>
       <c r="D46" s="29">
-        <f t="shared" ref="D46:L46" si="1">SUM(D44:D45)</f>
+        <f t="shared" ref="D46:L46" si="3">SUM(D44:D45)</f>
         <v>945425</v>
       </c>
       <c r="E46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1015225</v>
       </c>
       <c r="F46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2788779.67</v>
       </c>
       <c r="G46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2714291.67</v>
       </c>
       <c r="H46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2642288</v>
       </c>
       <c r="I46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2572685</v>
       </c>
       <c r="J46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2505400</v>
       </c>
       <c r="K46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2440360</v>
       </c>
       <c r="L46" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2377486</v>
       </c>
     </row>
@@ -11244,39 +11243,39 @@
     <row r="52" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="28"/>
       <c r="D52" s="29">
-        <f t="shared" ref="D52:L52" si="2">SUM(D51)</f>
+        <f t="shared" ref="D52:L52" si="4">SUM(D51)</f>
         <v>0</v>
       </c>
       <c r="E52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>348030</v>
       </c>
       <c r="G52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L52" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>818728.93</v>
       </c>
     </row>
@@ -11384,39 +11383,39 @@
     <row r="59" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="28"/>
       <c r="D59" s="29">
-        <f t="shared" ref="D59:L59" si="3">SUM(D57)+D58</f>
+        <f t="shared" ref="D59:L59" si="5">SUM(D57)+D58</f>
         <v>0</v>
       </c>
       <c r="E59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1213698.93</v>
       </c>
       <c r="F59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L59" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -11538,39 +11537,39 @@
     <row r="66" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="30"/>
       <c r="D66" s="31">
-        <f t="shared" ref="D66:L66" si="4">SUM(D64:D65)</f>
+        <f t="shared" ref="D66:L66" si="6">SUM(D64:D65)</f>
         <v>58249420</v>
       </c>
       <c r="E66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>26125591.969999999</v>
       </c>
       <c r="F66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>57533471.969999999</v>
       </c>
       <c r="G66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>27135001.969999999</v>
       </c>
       <c r="H66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>146282641.97</v>
       </c>
       <c r="I66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>308870521.97000003</v>
       </c>
       <c r="J66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>44008441.969999999</v>
       </c>
       <c r="K66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>47056991.969999999</v>
       </c>
       <c r="L66" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>257918170.90000001</v>
       </c>
     </row>
@@ -11655,39 +11654,39 @@
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="30"/>
       <c r="D71" s="31">
-        <f t="shared" ref="D71:L71" si="5">D70</f>
+        <f t="shared" ref="D71:L71" si="7">D70</f>
         <v>0</v>
       </c>
       <c r="E71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L71" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -11896,39 +11895,39 @@
     <row r="80" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="30"/>
       <c r="D80" s="31">
-        <f t="shared" ref="D80:L80" si="6">SUM(D75:D79)</f>
+        <f t="shared" ref="D80:L80" si="8">SUM(D75:D79)</f>
         <v>83741326.550000012</v>
       </c>
       <c r="E80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>85493924.780000001</v>
       </c>
       <c r="F80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>61824407.670000002</v>
       </c>
       <c r="G80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>62018423.910000004</v>
       </c>
       <c r="H80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>48853984.040000007</v>
       </c>
       <c r="I80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>49709541.409999996</v>
       </c>
       <c r="J80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>52328164.57</v>
       </c>
       <c r="K80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>39580197.519999996</v>
       </c>
       <c r="L80" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>40815031.68</v>
       </c>
     </row>
@@ -12012,39 +12011,39 @@
     <row r="86" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="30"/>
       <c r="D86" s="31">
-        <f t="shared" ref="D86:L86" si="7">D85</f>
+        <f t="shared" ref="D86:L86" si="9">D85</f>
         <v>0</v>
       </c>
       <c r="E86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>261063780</v>
       </c>
       <c r="K86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>267758882</v>
       </c>
       <c r="L86" s="31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>454383984</v>
       </c>
     </row>
@@ -12552,39 +12551,39 @@
     <row r="106" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C106" s="30"/>
       <c r="D106" s="31">
-        <f t="shared" ref="D106:L106" si="8">SUM(D94:D100)-SUM(D101:D105)</f>
+        <f t="shared" ref="D106:L106" si="10">SUM(D94:D100)-SUM(D101:D105)</f>
         <v>698099575</v>
       </c>
       <c r="E106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>728876350</v>
       </c>
       <c r="F106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>726101070.33000004</v>
       </c>
       <c r="G106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>763386778.65999997</v>
       </c>
       <c r="H106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>810744490.65999997</v>
       </c>
       <c r="I106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1098229805.6600001</v>
       </c>
       <c r="J106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1096364405.6600001</v>
       </c>
       <c r="K106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1095978345.6600001</v>
       </c>
       <c r="L106" s="31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1144673859.6600001</v>
       </c>
     </row>
@@ -12666,39 +12665,39 @@
     <row r="111" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C111" s="30"/>
       <c r="D111" s="31">
-        <f t="shared" ref="D111:L111" si="9">D110</f>
+        <f t="shared" ref="D111:L111" si="11">D110</f>
         <v>839530823.44000006</v>
       </c>
       <c r="E111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>839530823.44000006</v>
       </c>
       <c r="F111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>839530823.44000006</v>
       </c>
       <c r="G111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>839530823.44000006</v>
       </c>
       <c r="H111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>989530823.44000006</v>
       </c>
       <c r="I111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1439530823.4400001</v>
       </c>
       <c r="J111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1439530823.4400001</v>
       </c>
       <c r="K111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1439530823.4400001</v>
       </c>
       <c r="L111" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1889530823.4400001</v>
       </c>
     </row>
@@ -15361,7 +15360,7 @@
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="49"/>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="97" t="s">
         <v>111</v>
       </c>
       <c r="C7" s="96"/>
@@ -15383,10 +15382,10 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="49"/>
-      <c r="B8" s="97" t="b">
+      <c r="B8" s="106" t="b">
         <v>1</v>
       </c>
-      <c r="C8" s="98" t="str">
+      <c r="C8" s="100" t="str">
         <f>PROPER(B24)</f>
         <v>Revenue</v>
       </c>
@@ -15428,10 +15427,10 @@
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="49"/>
-      <c r="B10" s="97" t="b">
+      <c r="B10" s="106" t="b">
         <v>1</v>
       </c>
-      <c r="C10" s="98" t="str">
+      <c r="C10" s="100" t="str">
         <f>PROPER(B25)</f>
         <v>Cost Of Goods Sold</v>
       </c>
@@ -15473,10 +15472,10 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="49"/>
-      <c r="B12" s="97" t="b">
+      <c r="B12" s="106" t="b">
         <v>1</v>
       </c>
-      <c r="C12" s="98" t="str">
+      <c r="C12" s="100" t="str">
         <f>PROPER(B26)</f>
         <v>Total Expenses</v>
       </c>
@@ -15518,10 +15517,10 @@
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="58"/>
-      <c r="B14" s="97" t="b">
+      <c r="B14" s="106" t="b">
         <v>1</v>
       </c>
-      <c r="C14" s="98" t="str">
+      <c r="C14" s="100" t="str">
         <f>PROPER(B27)</f>
         <v>Net Profit / Loss</v>
       </c>
@@ -15583,7 +15582,7 @@
     </row>
     <row r="17" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="65"/>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="107" t="s">
         <v>112</v>
       </c>
       <c r="C17" s="96"/>
@@ -15641,7 +15640,7 @@
     </row>
     <row r="18" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="65"/>
-      <c r="B18" s="100" t="s">
+      <c r="B18" s="105" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="96"/>
@@ -15687,7 +15686,7 @@
     </row>
     <row r="19" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="65"/>
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="105" t="s">
         <v>157</v>
       </c>
       <c r="C19" s="96"/>
@@ -15733,7 +15732,7 @@
     </row>
     <row r="20" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="65"/>
-      <c r="B20" s="100" t="s">
+      <c r="B20" s="105" t="s">
         <v>158</v>
       </c>
       <c r="C20" s="96"/>
@@ -15779,7 +15778,7 @@
     </row>
     <row r="21" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="65"/>
-      <c r="B21" s="100" t="s">
+      <c r="B21" s="105" t="s">
         <v>159</v>
       </c>
       <c r="C21" s="96"/>
@@ -15825,7 +15824,7 @@
     </row>
     <row r="22" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="65"/>
-      <c r="B22" s="101"/>
+      <c r="B22" s="98"/>
       <c r="C22" s="96"/>
       <c r="D22" s="69"/>
       <c r="E22" s="70"/>
@@ -15845,7 +15844,7 @@
     </row>
     <row r="23" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="71"/>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="104" t="s">
         <v>112</v>
       </c>
       <c r="C23" s="96"/>
@@ -15895,7 +15894,7 @@
     </row>
     <row r="24" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="65"/>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="97" t="s">
         <v>127</v>
       </c>
       <c r="C24" s="96"/>
@@ -15959,7 +15958,7 @@
     </row>
     <row r="25" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="65"/>
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="102" t="s">
         <v>128</v>
       </c>
       <c r="C25" s="96"/>
@@ -16023,7 +16022,7 @@
     </row>
     <row r="26" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="65"/>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="97" t="s">
         <v>129</v>
       </c>
       <c r="C26" s="96"/>
@@ -16087,7 +16086,7 @@
     </row>
     <row r="27" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="65"/>
-      <c r="B27" s="103" t="s">
+      <c r="B27" s="102" t="s">
         <v>130</v>
       </c>
       <c r="C27" s="96"/>
@@ -16151,7 +16150,7 @@
     </row>
     <row r="28" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="65"/>
-      <c r="B28" s="101"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="96"/>
       <c r="D28" s="81"/>
       <c r="E28" s="82"/>
@@ -16171,7 +16170,7 @@
     </row>
     <row r="29" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="71"/>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="104" t="s">
         <v>127</v>
       </c>
       <c r="C29" s="96"/>
@@ -16221,7 +16220,7 @@
     </row>
     <row r="30" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="65"/>
-      <c r="B30" s="98" t="s">
+      <c r="B30" s="100" t="s">
         <v>131</v>
       </c>
       <c r="C30" s="96"/>
@@ -16273,7 +16272,7 @@
     </row>
     <row r="31" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="65"/>
-      <c r="B31" s="104" t="s">
+      <c r="B31" s="95" t="s">
         <v>132</v>
       </c>
       <c r="C31" s="96"/>
@@ -16325,7 +16324,7 @@
     </row>
     <row r="32" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
-      <c r="B32" s="98" t="s">
+      <c r="B32" s="100" t="s">
         <v>133</v>
       </c>
       <c r="C32" s="96"/>
@@ -16377,7 +16376,7 @@
     </row>
     <row r="33" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="65"/>
-      <c r="B33" s="104" t="s">
+      <c r="B33" s="95" t="s">
         <v>134</v>
       </c>
       <c r="C33" s="96"/>
@@ -16429,7 +16428,7 @@
     </row>
     <row r="34" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="65"/>
-      <c r="B34" s="95" t="str">
+      <c r="B34" s="97" t="str">
         <f>"TOTAL "&amp;C29</f>
         <v xml:space="preserve">TOTAL </v>
       </c>
@@ -16494,7 +16493,7 @@
     </row>
     <row r="35" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="65"/>
-      <c r="B35" s="101"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="96"/>
       <c r="D35" s="81"/>
       <c r="E35" s="82"/>
@@ -16514,7 +16513,7 @@
     </row>
     <row r="36" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="65"/>
-      <c r="B36" s="102" t="s">
+      <c r="B36" s="104" t="s">
         <v>128</v>
       </c>
       <c r="C36" s="96"/>
@@ -16564,7 +16563,7 @@
     </row>
     <row r="37" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="86"/>
-      <c r="B37" s="98" t="s">
+      <c r="B37" s="100" t="s">
         <v>135</v>
       </c>
       <c r="C37" s="96"/>
@@ -16616,7 +16615,7 @@
     </row>
     <row r="38" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="86"/>
-      <c r="B38" s="104" t="s">
+      <c r="B38" s="95" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="96"/>
@@ -16668,7 +16667,7 @@
     </row>
     <row r="39" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="86"/>
-      <c r="B39" s="98" t="s">
+      <c r="B39" s="100" t="s">
         <v>137</v>
       </c>
       <c r="C39" s="96"/>
@@ -16720,7 +16719,7 @@
     </row>
     <row r="40" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="86"/>
-      <c r="B40" s="104" t="s">
+      <c r="B40" s="95" t="s">
         <v>138</v>
       </c>
       <c r="C40" s="96"/>
@@ -16772,7 +16771,7 @@
     </row>
     <row r="41" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="86"/>
-      <c r="B41" s="98" t="s">
+      <c r="B41" s="100" t="s">
         <v>139</v>
       </c>
       <c r="C41" s="96"/>
@@ -16824,7 +16823,7 @@
     </row>
     <row r="42" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="65"/>
-      <c r="B42" s="104" t="s">
+      <c r="B42" s="95" t="s">
         <v>140</v>
       </c>
       <c r="C42" s="96"/>
@@ -16876,7 +16875,7 @@
     </row>
     <row r="43" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="65"/>
-      <c r="B43" s="98" t="s">
+      <c r="B43" s="100" t="s">
         <v>141</v>
       </c>
       <c r="C43" s="96"/>
@@ -16928,7 +16927,7 @@
     </row>
     <row r="44" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="65"/>
-      <c r="B44" s="103" t="str">
+      <c r="B44" s="102" t="str">
         <f>"TOTAL "&amp;C36</f>
         <v xml:space="preserve">TOTAL </v>
       </c>
@@ -16993,7 +16992,7 @@
     </row>
     <row r="45" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="65"/>
-      <c r="B45" s="101"/>
+      <c r="B45" s="98"/>
       <c r="C45" s="96"/>
       <c r="D45" s="81"/>
       <c r="E45" s="82"/>
@@ -17013,7 +17012,7 @@
     </row>
     <row r="46" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="65"/>
-      <c r="B46" s="105" t="s">
+      <c r="B46" s="103" t="s">
         <v>142</v>
       </c>
       <c r="C46" s="96"/>
@@ -17077,7 +17076,7 @@
     </row>
     <row r="47" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="65"/>
-      <c r="B47" s="101"/>
+      <c r="B47" s="98"/>
       <c r="C47" s="96"/>
       <c r="D47" s="81"/>
       <c r="E47" s="89"/>
@@ -17097,7 +17096,7 @@
     </row>
     <row r="48" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="65"/>
-      <c r="B48" s="106" t="s">
+      <c r="B48" s="101" t="s">
         <v>143</v>
       </c>
       <c r="C48" s="96"/>
@@ -17147,7 +17146,7 @@
     </row>
     <row r="49" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="86"/>
-      <c r="B49" s="98" t="s">
+      <c r="B49" s="100" t="s">
         <v>144</v>
       </c>
       <c r="C49" s="96"/>
@@ -17199,7 +17198,7 @@
     </row>
     <row r="50" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="86"/>
-      <c r="B50" s="104" t="s">
+      <c r="B50" s="95" t="s">
         <v>145</v>
       </c>
       <c r="C50" s="96"/>
@@ -17251,7 +17250,7 @@
     </row>
     <row r="51" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="86"/>
-      <c r="B51" s="98" t="s">
+      <c r="B51" s="100" t="s">
         <v>146</v>
       </c>
       <c r="C51" s="96"/>
@@ -17303,7 +17302,7 @@
     </row>
     <row r="52" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="86"/>
-      <c r="B52" s="104" t="s">
+      <c r="B52" s="95" t="s">
         <v>147</v>
       </c>
       <c r="C52" s="96"/>
@@ -17355,7 +17354,7 @@
     </row>
     <row r="53" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="86"/>
-      <c r="B53" s="98" t="s">
+      <c r="B53" s="100" t="s">
         <v>148</v>
       </c>
       <c r="C53" s="96"/>
@@ -17407,7 +17406,7 @@
     </row>
     <row r="54" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="86"/>
-      <c r="B54" s="104" t="s">
+      <c r="B54" s="95" t="s">
         <v>149</v>
       </c>
       <c r="C54" s="96"/>
@@ -17459,7 +17458,7 @@
     </row>
     <row r="55" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="86"/>
-      <c r="B55" s="98" t="s">
+      <c r="B55" s="100" t="s">
         <v>150</v>
       </c>
       <c r="C55" s="96"/>
@@ -17511,7 +17510,7 @@
     </row>
     <row r="56" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="86"/>
-      <c r="B56" s="104" t="s">
+      <c r="B56" s="95" t="s">
         <v>151</v>
       </c>
       <c r="C56" s="96"/>
@@ -17563,7 +17562,7 @@
     </row>
     <row r="57" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="86"/>
-      <c r="B57" s="98" t="s">
+      <c r="B57" s="100" t="s">
         <v>152</v>
       </c>
       <c r="C57" s="96"/>
@@ -17615,7 +17614,7 @@
     </row>
     <row r="58" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="86"/>
-      <c r="B58" s="104" t="s">
+      <c r="B58" s="95" t="s">
         <v>153</v>
       </c>
       <c r="C58" s="96"/>
@@ -17667,7 +17666,7 @@
     </row>
     <row r="59" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="86"/>
-      <c r="B59" s="98" t="s">
+      <c r="B59" s="100" t="s">
         <v>154</v>
       </c>
       <c r="C59" s="96"/>
@@ -17719,7 +17718,7 @@
     </row>
     <row r="60" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="86"/>
-      <c r="B60" s="104" t="s">
+      <c r="B60" s="95" t="s">
         <v>155</v>
       </c>
       <c r="C60" s="96"/>
@@ -17771,7 +17770,7 @@
     </row>
     <row r="61" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="65"/>
-      <c r="B61" s="95" t="str">
+      <c r="B61" s="97" t="str">
         <f>"TOTAL "&amp;C48</f>
         <v xml:space="preserve">TOTAL </v>
       </c>
@@ -17836,7 +17835,7 @@
     </row>
     <row r="62" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="65"/>
-      <c r="B62" s="101"/>
+      <c r="B62" s="98"/>
       <c r="C62" s="96"/>
       <c r="D62" s="81"/>
       <c r="E62" s="90"/>
@@ -17856,7 +17855,7 @@
     </row>
     <row r="63" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="74"/>
-      <c r="B63" s="107" t="s">
+      <c r="B63" s="99" t="s">
         <v>156</v>
       </c>
       <c r="C63" s="96"/>
@@ -18876,6 +18875,51 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B62:C62"/>
@@ -18887,51 +18931,6 @@
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <conditionalFormatting sqref="E24:Q27 E30:Q34 E37:Q44 E46:Q64 D48">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
